--- a/AAII_Financials/Quarterly/CAG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAG_QTR_FIN.xlsx
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46075</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45984</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45893</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45802</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45711</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45620</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45529</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45438</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45347</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45256</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45165</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45074</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44983</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44892</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44801</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44710</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44619</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44528</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44437</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44346</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44164</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44073</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43884</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43793</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43702</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43611</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43520</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43429</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43338</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43156</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43065</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42974</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42883</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42792</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42701</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2882100</v>
+      </c>
+      <c r="E8" s="3">
         <v>2787800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2979100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2632600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2781800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2841000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3195100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2794900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2905900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3032900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3208100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2904000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2973300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3086500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3312900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2904300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2910000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2913700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3058900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2653300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2739500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2771100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2995200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2678900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3287900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2555000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2820800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2390700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2613200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2707100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2383700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1834400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1966200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1994500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2173400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1804200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1861700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1981200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2088400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1895600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2176400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2130100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2283100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1991300</v>
       </c>
-      <c r="G9" s="3">
-        <v>2073600</v>
-      </c>
       <c r="H9" s="3">
+        <v>2074600</v>
+      </c>
+      <c r="I9" s="3">
         <v>2130700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2348400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2058900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2101000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2174100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2361500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2080900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2189900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2247700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2382500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2181200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2187500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2207300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2294200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1971400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2009800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2003500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2096800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1858300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2354500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1854000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2015800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1714400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1897500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1951000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1708800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1310100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1382800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1396300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1514700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1275500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1330800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1355200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1436100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1345500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>705700</v>
+      </c>
+      <c r="E10" s="3">
         <v>657700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>696000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>641300</v>
       </c>
-      <c r="G10" s="3">
-        <v>708200</v>
-      </c>
       <c r="H10" s="3">
+        <v>707200</v>
+      </c>
+      <c r="I10" s="3">
         <v>710300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>846700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>736000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>804900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>858800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>846600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>823100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>783400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>838800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>930400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>723100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>722500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>706400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>764700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>681900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>729700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>767600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>898400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>820600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>933400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>701000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>805000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>676300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>715700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>756100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>674900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>524300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>583400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>598200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>658700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>528700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>530900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>626000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>652300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>550100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,13 +1248,14 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>62700</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1249,11 +1263,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>60800</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1261,11 +1275,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>61400</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1273,11 +1287,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>57700</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,175 +1496,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2027600</v>
+      </c>
+      <c r="E14" s="3">
         <v>8400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>931500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-40400</v>
       </c>
-      <c r="G14" s="3">
-        <v>43500</v>
-      </c>
       <c r="H14" s="3">
+        <v>45900</v>
+      </c>
+      <c r="I14" s="3">
         <v>155800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>92200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>975100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>36400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>45600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>20100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>366500</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>419900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>219200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>47400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>37000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>17900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>104700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>60200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>26600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>175300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>31800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>29400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>103800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>32600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>14600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>200500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>52100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>14900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>11400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>44500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>47200</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>322000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-20500</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E15" s="3">
         <v>101400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>97000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>94900</v>
       </c>
-      <c r="G15" s="3">
-        <v>95000</v>
-      </c>
       <c r="H15" s="3">
+        <v>95300</v>
+      </c>
+      <c r="I15" s="3">
         <v>98300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>97500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>99100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>95800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>99300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>96600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>92900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>91500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2485200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2493200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2639100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2319500</v>
       </c>
-      <c r="G17" s="3">
-        <v>2400700</v>
-      </c>
       <c r="H17" s="3">
+        <v>2398300</v>
+      </c>
+      <c r="I17" s="3">
         <v>2442700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2697200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2388500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2474500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2526500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2714400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2395200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2543800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2590500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2757200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2919500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2676900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2538400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2636700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2273900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2439800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2308700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2450300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2155200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2924000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2168400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2381900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2110200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2284000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2296900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2186400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1559500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1827100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1726400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1825400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1517100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1754200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1711000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1853300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1581200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>396900</v>
+      </c>
+      <c r="E18" s="3">
         <v>294600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>340000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>313100</v>
       </c>
-      <c r="G18" s="3">
-        <v>381100</v>
-      </c>
       <c r="H18" s="3">
+        <v>383500</v>
+      </c>
+      <c r="I18" s="3">
         <v>398300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>497900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>406400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>431400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>506400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>493700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>508800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>429500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>496000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>555700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>233100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>375300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>422200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>379400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>299700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>462400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>544900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>523700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>363900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>386600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>438900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>280500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>329200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>410200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>197300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>274900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>139100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>268100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>348000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>287100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>107500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>270200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>235100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>314400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-36500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-32200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-29400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-57400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-47400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-48500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-29100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-46600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-41200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-54300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-35500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-63000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-50500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3600</v>
-      </c>
-      <c r="V20" s="3">
-        <v>300</v>
       </c>
       <c r="W20" s="3">
         <v>300</v>
       </c>
       <c r="X20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y20" s="3">
         <v>400</v>
       </c>
       <c r="Z20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>19700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>4100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>541700</v>
+      </c>
+      <c r="E21" s="3">
         <v>432500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>469200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>437400</v>
       </c>
-      <c r="G21" s="3">
-        <v>533500</v>
-      </c>
       <c r="H21" s="3">
+        <v>536200</v>
+      </c>
+      <c r="I21" s="3">
         <v>544000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>643900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>534600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>587200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>643400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>647300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>640900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>585400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>638000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>648800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>78700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>323900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>467900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>522800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>476200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>398100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>559400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>643100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>619700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>460700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>481300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>536500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>370500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>420900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>522200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>278700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>332700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>198500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>333800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>416400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>345600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>180300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>338600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>296700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>380800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>94600</v>
+      </c>
+      <c r="E22" s="3">
         <v>95400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>99800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>96400</v>
       </c>
-      <c r="G22" s="3">
-        <v>102400</v>
-      </c>
       <c r="H22" s="3">
+        <v>96000</v>
+      </c>
+      <c r="I22" s="3">
         <v>103400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>108800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>106700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>107100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>107900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>113300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>107100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>109300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>105300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>98000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>97200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>95100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>95200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>94500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>98700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>101000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>108100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>114500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>126100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>119000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>121800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>123300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>132700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>132800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>83100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>49600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>45500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>40600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>39100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>37300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>38400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>46700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>54900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>58900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1687800</v>
+      </c>
+      <c r="E23" s="3">
         <v>229600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-655300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>289100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>293200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>189000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>346000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>328000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-601800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>404700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>389100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>418200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>442300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>455400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-112300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>136900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>280700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>330600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>285200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>201300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>361800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>437200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>410000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>238200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>263200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>318000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>150500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>187800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>297100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>119000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>219400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>89400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>228800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>313000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>243600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>73700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>225600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>175500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>254700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-70900</v>
+      </c>
+      <c r="E24" s="3">
         <v>29800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>37200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>43900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-138900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-34600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>95900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>102900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>98300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-18300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>122500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>109900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>84200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>69700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-75200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>101600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>80700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>86700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>59800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>68900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>84100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>71800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>67200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>22400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>57400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>33100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>145300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>109500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>120000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-60800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>67900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>78400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>169200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1616900</v>
+      </c>
+      <c r="E26" s="3">
         <v>199800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-663600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>164500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>256000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>145100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>284500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>466900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-567200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>308800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>286200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>319900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>342200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>332900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-126700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>110200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>170800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>246400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>215500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>276500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>260200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>356500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>323300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>178400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>194300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>233900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>162000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>116000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>229900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>96600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>162000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>56300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>83500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>203500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>123600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>134500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>157700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>97100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>85500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1616900</v>
+      </c>
+      <c r="E27" s="3">
         <v>199800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-663600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>164500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>256000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>145100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>284500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>466800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-567300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>308600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>286200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>319700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>341700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>381900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-77500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>158900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>218400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>275500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>235400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>309500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>281400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>378900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>329000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>201400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>204400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>260500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>173800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>126500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>242000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>133500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>178200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>73300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>111600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>223100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>152800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>153000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>179000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>110200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>94300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3233,47 +3294,50 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>251200</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>400</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-300</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>700</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>11600</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E32" s="3">
         <v>36500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>32200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>29400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>57400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>47400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>48500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>29100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>46600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>41200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>54300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>35500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>63000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>50500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3600</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-300</v>
       </c>
       <c r="W32" s="3">
         <v>-300</v>
       </c>
       <c r="X32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="Y32" s="3">
         <v>-400</v>
       </c>
       <c r="Z32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-19700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>6200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>4700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1616900</v>
+      </c>
+      <c r="E33" s="3">
         <v>199800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-663600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>164500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>256000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>145100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>284500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>466800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-567300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>308600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>286200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>319700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>341700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>381900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-77500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>158900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>218400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>275500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>235400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>309500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>281400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>378900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>329000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>201400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>204400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>260500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>173800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>126500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>242000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>131600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>178200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>362800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>223500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>152500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>151300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>179700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>121800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1616900</v>
+      </c>
+      <c r="E35" s="3">
         <v>199800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-663600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>164500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>256000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>145100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>284500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>466800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-567300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>308600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>286200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>319700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>341700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>381900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-77500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>158900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>218400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>275500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>235400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>309500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>281400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>378900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>329000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>201400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>204400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>260500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>173800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>126500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>242000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>131600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>178200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>362800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>223500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>152500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>151300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>179700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>121800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46075</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45984</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45893</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45802</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45711</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45620</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45529</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45438</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45347</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45256</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45165</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45074</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44983</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44892</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44801</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44710</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44619</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44528</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44437</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44346</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44164</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44073</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43884</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43793</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43702</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43611</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43520</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43429</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43338</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43156</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43065</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42974</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42883</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42792</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42701</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E41" s="3">
         <v>55100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>698100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>128700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>61500</v>
-      </c>
-      <c r="N41" s="3">
-        <v>93300</v>
       </c>
       <c r="O41" s="3">
         <v>93300</v>
       </c>
       <c r="P41" s="3">
+        <v>93300</v>
+      </c>
+      <c r="Q41" s="3">
         <v>71200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>39700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>67400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>83300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>79700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>67000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>80700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>68000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>438200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>553300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>99000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>192000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>64700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>236600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>282200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>442300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>74800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>128000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>132900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>84000</v>
-      </c>
-      <c r="AL41" s="3">
-        <v>251400</v>
       </c>
       <c r="AM41" s="3">
         <v>251400</v>
       </c>
       <c r="AN41" s="3">
+        <v>251400</v>
+      </c>
+      <c r="AO41" s="3">
         <v>683600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1442500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>794600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4437,283 +4527,292 @@
         <v>0</v>
       </c>
       <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
         <v>2800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2800</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>27200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>26500</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>658200</v>
+      </c>
+      <c r="E43" s="3">
         <v>757000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>835500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>756500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>770000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>715300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>856900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>933400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>871800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>916500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>974100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>971500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>952800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>960000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>910500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>788600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>867400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>914500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>977200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>834400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>793900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>841400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>948500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>807800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>860800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>854200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>947600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>776300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>831700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>870200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>958100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>599200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>569400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>603400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>683800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>577100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>563400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>601400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>699500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>847000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1905400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1943600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2199800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2258200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2048300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1954500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2180800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2220600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1981500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2143400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2277600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2393800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2212200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2307100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2347700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2229400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1939700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1766500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1858700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1954600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1734000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1579200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1622800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1579600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1377900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1646500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1770400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1755700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1571700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1638600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1729700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1108500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>988700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1016700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1059200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1068800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>934200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1046400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1113700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1637900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>6300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4721,243 +4820,249 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>99800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>136000</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>139200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>30200</v>
       </c>
       <c r="M45" s="3">
         <v>30200</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="N45" s="3">
+        <v>30200</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>57300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>118500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>148400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>143300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>153900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>134700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>116200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>95000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>126600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>158400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>109500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>93900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>109700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>119600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>131300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>93800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>155100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>145300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>261200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>247000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>303000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>225000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>222300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>261400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>204000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>62100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>101100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2882100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2890800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3226300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3840100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3071000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2965600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3205400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3416200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3149500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3285800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3469100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3573500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3385000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3454700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3416400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3233800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3033700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2914600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3039300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2972200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2702100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2627900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2797700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2935100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2885900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2709400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3029600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2728000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2733800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2946100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3275400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2046500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1938900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2058100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2056300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2125000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2013200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2539100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3345000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3407100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>947400</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -4965,11 +5070,11 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>936800</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -4977,11 +5082,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>931700</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -4989,15 +5094,15 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>998400</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3033600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2800600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2801700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2815800</v>
       </c>
-      <c r="G48" s="3">
-        <v>3045600</v>
-      </c>
       <c r="H48" s="3">
+        <v>3036300</v>
+      </c>
+      <c r="I48" s="3">
         <v>2739000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2820300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2877000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2992300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2876700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2876500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2914600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2933900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2702000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2688200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2704600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2921500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2655500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2622800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2646200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2797000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2526800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2478000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2430700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2598900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2539200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2557200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2577300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2395300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2358600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2360800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1636300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1589500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1627300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1642000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1647300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1664900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1655800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1669300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2736800</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9950000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11922500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11931700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12911800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12923000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12986900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13481000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13514400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12810700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14262000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14274700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14370600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14301700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14742600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14759100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14776800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15182300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15410000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15424200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>15509900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>15531100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>15659200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15672200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15742500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15752000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15922500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15937000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15987100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>16161000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>16311800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>16299400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5774600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5770200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5807100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5755200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5525300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5531200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5504800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5509600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5634100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>461300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1598400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1580600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1605100</v>
       </c>
-      <c r="G52" s="3">
-        <v>957500</v>
-      </c>
       <c r="H52" s="3">
+        <v>966800</v>
+      </c>
+      <c r="I52" s="3">
         <v>2053000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1511400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1440200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>978100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1495400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1499700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1506700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>433600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1554900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1550300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1504300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1297600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1519200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1505700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1411600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1165400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1291200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1328800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1269000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1067200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1031000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>968800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1062100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>923700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1110100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1071200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1027600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1090900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>970700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>946600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>928000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>887000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>799300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>901100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1057900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17274400</v>
+      </c>
+      <c r="E54" s="3">
         <v>19212300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19540300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21172800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20933900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20744500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21018100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21247800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20862300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21919900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22120000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22365400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22052600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22454200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22414000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22219500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22435100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22499300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22592000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22539900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22195600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22105100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22276700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22377300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22304000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22202100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>22492600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22354500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22213800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22726600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23006800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>10485000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10389500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10463200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>10400100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>10225600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10096300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10499000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>11425000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>12835900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1513300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1416800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1526900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1532500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1590100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1421400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1571700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1537700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1493700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1418000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1474600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1534600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1525500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1563900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1596300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1851300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1864600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1593900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1596900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1674400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1655900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1442700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1598100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1523300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1525600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1357400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1441600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1316900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1255300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1189200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1246100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>984000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>905300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>869600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>886700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>845700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>773100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>690100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>784100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>992900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>848400</v>
+      </c>
+      <c r="E58" s="3">
         <v>875300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1164900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1057200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1873200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1908300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2225800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1286600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>985400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1185500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1576300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1528500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2194400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1174600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1319800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1458100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>891600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1069100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>856400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>480500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>730500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>949300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>987000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>719200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>846600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>924600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1174300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>206100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>21600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>18100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>611600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>584300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>429600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>265900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>522200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>227200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>132500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>237700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>522700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E59" s="3">
         <v>47800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>151400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>169100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>162200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>23500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>806600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>850900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>762600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>861600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>823700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>935400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>919800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>899100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>766300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>859400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>915200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>845100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>809900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>926900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>865700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1032600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>970300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>837800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>846600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>691500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>697700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>685700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>720200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>742300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>723600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>849200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3188000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3208100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3619700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3629600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4317000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4303700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4559700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3646800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3241800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3470900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3833100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3940100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4440700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3561000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3722700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4160300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3518800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3524600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3277000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3090300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3306200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3291100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3351400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3101900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3287400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3127100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3425800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2449900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2142600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2241700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2234500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2433400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2336200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1990700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1850300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2053600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1720500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1564900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1745400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2364800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6626700</v>
+      </c>
+      <c r="E61" s="3">
         <v>6457100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6459000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7222600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6437400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6236800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6237800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7485600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7661900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7491800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7493300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7745100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7266900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8318900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8081800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7584100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8088200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8089100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8527800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8779600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8275200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8278100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8279700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8897600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8900800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9093700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9295900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10323400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10655700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11107700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11545400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3233700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3231500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3232900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3261800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2767000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2769200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2841700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3214300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4451400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>296200</v>
+      </c>
+      <c r="E62" s="3">
         <v>594800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>586800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>594200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>314400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1424900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1419900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1419800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>295100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1731700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1719400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1725100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1400000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1636000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1871800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1898400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1965900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2032300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2030300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2034100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1982800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2206100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2176100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2178800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2165100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2117400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2080300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2064400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1951800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1925700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1923600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1002900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1430100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1501500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1522400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1528800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1788200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1938500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2220100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10916800</v>
+      </c>
+      <c r="E66" s="3">
         <v>11048200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11449500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12257000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12001200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11965400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12217400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12552200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12351000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12694400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13045800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13410300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13245300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13515900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13747700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13715200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13647400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13724700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13913000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13982900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13643800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13853300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13884700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14255900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14427900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14417100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14880500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14914400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14829200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15353600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15782700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6748500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6713300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6742700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6702400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6431800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6105500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6277700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6978300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>9117600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4171700</v>
+      </c>
+      <c r="E72" s="3">
         <v>5955600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5924300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6755900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6759100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6669900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6692000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6574800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6276300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7011700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6871500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6752900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6599400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6720000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6536500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6314800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6550700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6541200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6473300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6348300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6262600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6086700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5938700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5694600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5471200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5375200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5274700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5118000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5047900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5025300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4886400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4841500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4744900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4758800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4464300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4312600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4247000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4171000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4077300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3290700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6357600</v>
+      </c>
+      <c r="E76" s="3">
         <v>8164100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8090800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8915800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8932700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8779100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8800700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8695600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8440400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9154900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9004000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8884500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8736800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8866400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8666300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8504300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8787700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8774600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8679000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8557000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8551800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8251800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8392000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8121400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7876100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7785000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7612100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7440100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7384600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7373000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7224100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3736500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3676200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3720500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3697700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3793800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3990800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4221300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4446700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3718300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46075</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45984</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45893</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45802</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45711</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45620</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45529</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45438</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45347</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45256</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45165</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45074</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44983</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44892</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44801</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44710</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44619</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44528</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44437</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44346</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44164</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44073</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43884</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43793</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43702</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43611</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43520</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43429</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43338</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43156</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43065</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42974</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42883</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42792</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42701</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1616900</v>
+      </c>
+      <c r="E81" s="3">
         <v>199800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-663600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>164500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>256000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>145100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>284500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>466800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-567300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>308600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>286200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>319700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>341700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>381900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-77500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>158900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>218400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>275500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>235400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>309500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>281400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>378900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>329000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>201400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>204400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>260500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>173800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>126500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>242000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>131600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>178200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>362800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>223500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>152500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>151300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>179700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>121800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E83" s="3">
         <v>84800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>84000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>85700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>95800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>82400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>86000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>83100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>79400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>77700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>77800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>78200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>77300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>92500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>93000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>89800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>92100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>97000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>96500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>98100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>96600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>97800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>95200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>96400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>99100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>96700</v>
       </c>
       <c r="AD83" s="3">
         <v>96700</v>
       </c>
       <c r="AE83" s="3">
+        <v>96700</v>
+      </c>
+      <c r="AF83" s="3">
         <v>100400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>92300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>76600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>63700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>63600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>64400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>64300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>64700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>68200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>66300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>40800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>92700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>506500</v>
+      </c>
+      <c r="E89" s="3">
         <v>564400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>210600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>120600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>345700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>592000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>485600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>268600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>484300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>676700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>411100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>443500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>292000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>405600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>34100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>263700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>424700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>490500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>122300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>139800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>398100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>528600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>256900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>284500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>936100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>479000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>220500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>207000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>369200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>494400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>167200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>94700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>111900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>421600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>284700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>136000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>329000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>304300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>252700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>325900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-109200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-95600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-146800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-85100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-88800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-82400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-133000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-78500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-95600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-70400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-143600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-94800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-63000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-125400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-106700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-102600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-154900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-109700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-114700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-136500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-145500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-104200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-81600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-77100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-106600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-117000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-102800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-47200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-86100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-75700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-52500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-80800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-83600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-40200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>57200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-175500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-108500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-96100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>502000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-85000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-91200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-79700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-286300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-79400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-91700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-65500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-138400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-94700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-78300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-58500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-123400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-92000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-98700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-89300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-154900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-58400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-127600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-142900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-93900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>67300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>138300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-101800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5164000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-38500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-75000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-135100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-327500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-38600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-300500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-221700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>371900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,31 +10455,32 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E96" s="3">
         <v>167400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>167700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>167100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>167000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>167100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>167800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>167300</v>
       </c>
       <c r="K96" s="3">
         <v>167300</v>
@@ -10258,22 +10492,22 @@
         <v>167300</v>
       </c>
       <c r="N96" s="3">
-        <v>157400</v>
+        <v>167300</v>
       </c>
       <c r="O96" s="3">
         <v>157400</v>
       </c>
       <c r="P96" s="3">
+        <v>157400</v>
+      </c>
+      <c r="Q96" s="3">
         <v>157800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-158600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-149900</v>
       </c>
       <c r="T96" s="3">
         <v>-149900</v>
@@ -10282,70 +10516,73 @@
         <v>-149900</v>
       </c>
       <c r="V96" s="3">
+        <v>-149900</v>
+      </c>
+      <c r="W96" s="3">
         <v>-132100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-132900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-134400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-103800</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-103500</v>
       </c>
       <c r="AA96" s="3">
         <v>-103500</v>
       </c>
       <c r="AB96" s="3">
-        <v>-103400</v>
+        <v>-103500</v>
       </c>
       <c r="AC96" s="3">
         <v>-103400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-103300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-103200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-86700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-83300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-83000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-84600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-86100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-88300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-83300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-86100</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-109500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-109900</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-109500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-234600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-461600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-827100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-244000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-489100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-495300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>70100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-406400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-566900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-376300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-307100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-177100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-297100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-154400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-331000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-383300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-29200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-346000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-503600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-500400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-259600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-385800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-553100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-160700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-270800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-555600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-551300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>5366300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-109600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-38900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-237500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-123400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-107100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-462100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1026100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>656800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-737700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>9700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E102" s="3">
         <v>8500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-651500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>630100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-91300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>49700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>31500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-27700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-370200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-115100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>454300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>127300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-171900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-45600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-160100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>367500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-53200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>48900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-167400</v>
       </c>
-      <c r="AL102" s="3">
-        <v>0</v>
-      </c>
       <c r="AM102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="3">
         <v>-432200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-758900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>684300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-39900</v>
       </c>
     </row>
